--- a/public/exports-60-250/29189498.xlsx
+++ b/public/exports-60-250/29189498.xlsx
@@ -5014,7 +5014,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311241439</t>
+          <t xml:space="preserve">311241437</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
